--- a/exports/trend_1d/OBEROIRLTY_full_report.xlsx
+++ b/exports/trend_1d/OBEROIRLTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>10.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>277.55</v>
+        <v>269</v>
       </c>
       <c r="I2" t="n">
         <v>274.2127164314334</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>2.78</v>
+        <v>-0.39</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="M2" t="n">
         <v>0.62</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.37</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42132</v>
+        <v>42135</v>
       </c>
       <c r="H3" t="n">
-        <v>305.75</v>
+        <v>317.05</v>
       </c>
       <c r="I3" t="n">
         <v>308.2437434071924</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K3" t="n">
-        <v>-13.66</v>
+        <v>-17.86</v>
       </c>
       <c r="L3" t="n">
-        <v>19.7</v>
+        <v>21.93</v>
       </c>
       <c r="M3" t="n">
         <v>4.83</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>15.98</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42165</v>
+        <v>42166</v>
       </c>
       <c r="H4" t="n">
-        <v>285.1</v>
+        <v>281.35</v>
       </c>
       <c r="I4" t="n">
         <v>282.8525901695286</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>-10.08</v>
+        <v>-11.26</v>
       </c>
       <c r="L4" t="n">
-        <v>12.3</v>
+        <v>13.07</v>
       </c>
       <c r="M4" t="n">
         <v>0.58</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>16.16</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42262</v>
+        <v>42263</v>
       </c>
       <c r="H5" t="n">
-        <v>240.85</v>
+        <v>252.1</v>
       </c>
       <c r="I5" t="n">
         <v>248.9776573564458</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K5" t="n">
-        <v>14.39</v>
+        <v>10.4</v>
       </c>
       <c r="L5" t="n">
         <v>9.43</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.35</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42327</v>
+        <v>42328</v>
       </c>
       <c r="H6" t="n">
-        <v>264.64</v>
+        <v>259.35</v>
       </c>
       <c r="I6" t="n">
         <v>260.4019787618709</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.97</v>
+        <v>2.88</v>
       </c>
       <c r="L6" t="n">
         <v>5.18</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>12.23</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42369</v>
+        <v>42370</v>
       </c>
       <c r="H7" t="n">
-        <v>268.6</v>
+        <v>272.25</v>
       </c>
       <c r="I7" t="n">
         <v>270.5239298762459</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.57</v>
+        <v>-4.97</v>
       </c>
       <c r="L7" t="n">
-        <v>5.59</v>
+        <v>6.03</v>
       </c>
       <c r="M7" t="n">
         <v>1.5</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42388</v>
+        <v>42389</v>
       </c>
       <c r="H8" t="n">
-        <v>248.3</v>
+        <v>237.5</v>
       </c>
       <c r="I8" t="n">
         <v>245.5673378346083</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.800000000000001</v>
+        <v>-12.76</v>
       </c>
       <c r="L8" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
         <v>2.18</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>16.3</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>244.55</v>
+        <v>249.2</v>
       </c>
       <c r="I9" t="n">
         <v>247.799772532006</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.97</v>
+        <v>-4.93</v>
       </c>
       <c r="L9" t="n">
-        <v>5.24</v>
+        <v>5.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.86</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>14.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H10" t="n">
-        <v>338.7</v>
+        <v>301.3</v>
       </c>
       <c r="I10" t="n">
         <v>321.4868395152845</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K10" t="n">
-        <v>35.91</v>
+        <v>20.91</v>
       </c>
       <c r="L10" t="n">
         <v>7.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.86</v>
+        <v>14.38</v>
       </c>
       <c r="N10" t="n">
-        <v>5.19</v>
+        <v>11.04</v>
       </c>
       <c r="O10" t="n">
         <v>1.9</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>165</v>
+        <v>166</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>19.38</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42719</v>
+        <v>42720</v>
       </c>
       <c r="H11" t="n">
-        <v>312</v>
+        <v>329.55</v>
       </c>
       <c r="I11" t="n">
         <v>329.4905442619889</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.55</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>6.82</v>
+        <v>10.52</v>
       </c>
       <c r="M11" t="n">
         <v>3.53</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>18.01</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42908</v>
+        <v>42909</v>
       </c>
       <c r="H12" t="n">
-        <v>373.95</v>
+        <v>360.15</v>
       </c>
       <c r="I12" t="n">
         <v>368.239915415258</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K12" t="n">
-        <v>13.47</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>13.44</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.88</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42922</v>
+        <v>42923</v>
       </c>
       <c r="H13" t="n">
-        <v>364.4</v>
+        <v>382.35</v>
       </c>
       <c r="I13" t="n">
         <v>382.0457685123794</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.18</v>
+        <v>-6.16</v>
       </c>
       <c r="L13" t="n">
-        <v>4.35</v>
+        <v>6.75</v>
       </c>
       <c r="M13" t="n">
         <v>1.31</v>
       </c>
       <c r="N13" t="n">
-        <v>3.83</v>
+        <v>4.93</v>
       </c>
       <c r="O13" t="n">
         <v>-3.69</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.72</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43080</v>
+        <v>43081</v>
       </c>
       <c r="H14" t="n">
-        <v>455.3</v>
+        <v>451.05</v>
       </c>
       <c r="I14" t="n">
         <v>452.8952629031984</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K14" t="n">
-        <v>19.08</v>
+        <v>17.97</v>
       </c>
       <c r="L14" t="n">
         <v>8.98</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>11</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43108</v>
+        <v>43109</v>
       </c>
       <c r="H15" t="n">
-        <v>493.45</v>
+        <v>506.7</v>
       </c>
       <c r="I15" t="n">
         <v>494.0678615405957</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.4</v>
+        <v>-12.34</v>
       </c>
       <c r="L15" t="n">
-        <v>11.3</v>
+        <v>14.13</v>
       </c>
       <c r="M15" t="n">
         <v>4.06</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>8.24</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>521.7</v>
+        <v>490.25</v>
       </c>
       <c r="I16" t="n">
         <v>491.8876357435391</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>2.96</v>
+        <v>-3.25</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>5.06</v>
       </c>
       <c r="M16" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="N16" t="n">
-        <v>4.06</v>
+        <v>6.03</v>
       </c>
       <c r="O16" t="n">
         <v>2.69</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>16.44</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43154</v>
+        <v>43157</v>
       </c>
       <c r="H17" t="n">
-        <v>480.95</v>
+        <v>559.3</v>
       </c>
       <c r="I17" t="n">
         <v>529.5324921180486</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9</v>
+        <v>-14.08</v>
       </c>
       <c r="L17" t="n">
-        <v>5.46</v>
+        <v>17.16</v>
       </c>
       <c r="M17" t="n">
         <v>1.49</v>
       </c>
       <c r="N17" t="n">
-        <v>2.97</v>
+        <v>16.29</v>
       </c>
       <c r="O17" t="n">
         <v>-6.03</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>19.98</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43242</v>
+        <v>43243</v>
       </c>
       <c r="H18" t="n">
-        <v>512</v>
+        <v>499.7</v>
       </c>
       <c r="I18" t="n">
         <v>506.182316061021</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.460000000000001</v>
+        <v>-10.66</v>
       </c>
       <c r="L18" t="n">
         <v>16.5</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>15.78</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43396</v>
+        <v>43397</v>
       </c>
       <c r="H19" t="n">
-        <v>394.55</v>
+        <v>432.5</v>
       </c>
       <c r="I19" t="n">
         <v>425.6883750597117</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K19" t="n">
-        <v>21.04</v>
+        <v>13.45</v>
       </c>
       <c r="L19" t="n">
         <v>7.16</v>
@@ -1524,7 +1751,7 @@
         <v>3.81</v>
       </c>
       <c r="N19" t="n">
-        <v>4.61</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>-2.4</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>18.35</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H20" t="n">
-        <v>549.2</v>
+        <v>530.35</v>
       </c>
       <c r="I20" t="n">
         <v>534.4719857723906</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K20" t="n">
-        <v>26.98</v>
+        <v>22.62</v>
       </c>
       <c r="L20" t="n">
         <v>10.18</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>14.78</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H21" t="n">
-        <v>525.6</v>
+        <v>566.6</v>
       </c>
       <c r="I21" t="n">
         <v>558.1620368905063</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9</v>
+        <v>-6.84</v>
       </c>
       <c r="L21" t="n">
-        <v>4.54</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="N21" t="n">
-        <v>4.05</v>
+        <v>7.8</v>
       </c>
       <c r="O21" t="n">
         <v>-3.43</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>16.1</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43665</v>
+        <v>43668</v>
       </c>
       <c r="H22" t="n">
-        <v>561.85</v>
+        <v>549.2</v>
       </c>
       <c r="I22" t="n">
         <v>549.4138210806699</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.84</v>
+        <v>-3.07</v>
       </c>
       <c r="L22" t="n">
         <v>11.95</v>
       </c>
       <c r="M22" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="N22" t="n">
         <v>6.41</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.72</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43706</v>
+        <v>43707</v>
       </c>
       <c r="H23" t="n">
-        <v>549.5</v>
+        <v>567.95</v>
       </c>
       <c r="I23" t="n">
         <v>552.5018491601481</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.05</v>
+        <v>-3.41</v>
       </c>
       <c r="L23" t="n">
         <v>4.61</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>16.55</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43874</v>
+        <v>43875</v>
       </c>
       <c r="H24" t="n">
-        <v>517.3</v>
+        <v>507.1</v>
       </c>
       <c r="I24" t="n">
         <v>514.5222743790431</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.92</v>
+        <v>-10.71</v>
       </c>
       <c r="L24" t="n">
         <v>17.73</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43938</v>
+        <v>43941</v>
       </c>
       <c r="H25" t="n">
-        <v>385.35</v>
+        <v>391.7</v>
       </c>
       <c r="I25" t="n">
         <v>388.847705494162</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K25" t="n">
-        <v>24.01</v>
+        <v>22.76</v>
       </c>
       <c r="L25" t="n">
         <v>4.71</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>23.77</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43972</v>
+        <v>43973</v>
       </c>
       <c r="H26" t="n">
-        <v>300.9</v>
+        <v>292.9</v>
       </c>
       <c r="I26" t="n">
         <v>298.5762529252802</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.18</v>
+        <v>-25.22</v>
       </c>
       <c r="L26" t="n">
-        <v>24.69</v>
+        <v>25.96</v>
       </c>
       <c r="M26" t="n">
         <v>5.08</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>24.03</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H27" t="n">
-        <v>351.5</v>
+        <v>375.85</v>
       </c>
       <c r="I27" t="n">
         <v>362.6949085868123</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" t="n">
-        <v>-20.01</v>
+        <v>-28.32</v>
       </c>
       <c r="L27" t="n">
-        <v>21.82</v>
+        <v>31.24</v>
       </c>
       <c r="M27" t="n">
         <v>1.53</v>
       </c>
       <c r="N27" t="n">
-        <v>4.96</v>
+        <v>6.93</v>
       </c>
       <c r="O27" t="n">
         <v>-2.66</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>20.33</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H28" t="n">
-        <v>357.85</v>
+        <v>349.9</v>
       </c>
       <c r="I28" t="n">
         <v>351.9441268184921</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.79</v>
+        <v>-6.9</v>
       </c>
       <c r="L28" t="n">
         <v>8.41</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>14.54</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44069</v>
+        <v>44070</v>
       </c>
       <c r="H29" t="n">
-        <v>367.1</v>
+        <v>393.35</v>
       </c>
       <c r="I29" t="n">
         <v>389.7816720220084</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.92</v>
+        <v>-12.42</v>
       </c>
       <c r="L29" t="n">
         <v>14.86</v>
       </c>
       <c r="M29" t="n">
-        <v>1.52</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>7.15</v>
       </c>
       <c r="O29" t="n">
         <v>-2.22</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.25</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H30" t="n">
-        <v>536.7</v>
+        <v>518.35</v>
       </c>
       <c r="I30" t="n">
         <v>518.5931917198963</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K30" t="n">
-        <v>36.44</v>
+        <v>31.78</v>
       </c>
       <c r="L30" t="n">
         <v>6.81</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>17.89</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44274</v>
+        <v>44277</v>
       </c>
       <c r="H31" t="n">
-        <v>590</v>
+        <v>600.15</v>
       </c>
       <c r="I31" t="n">
         <v>597.7307311558318</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K31" t="n">
-        <v>-13.82</v>
+        <v>-15.78</v>
       </c>
       <c r="L31" t="n">
         <v>17.49</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.19</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H32" t="n">
-        <v>880.05</v>
+        <v>839.25</v>
       </c>
       <c r="I32" t="n">
         <v>863.8624480305859</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K32" t="n">
-        <v>46.64</v>
+        <v>39.84</v>
       </c>
       <c r="L32" t="n">
         <v>14.17</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>10</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>16.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H33" t="n">
-        <v>896</v>
+        <v>923.85</v>
       </c>
       <c r="I33" t="n">
         <v>907.9453594139262</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.76</v>
+        <v>-10.08</v>
       </c>
       <c r="L33" t="n">
-        <v>8.92</v>
+        <v>11.29</v>
       </c>
       <c r="M33" t="n">
         <v>1.54</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>12.74</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H34" t="n">
-        <v>932.85</v>
+        <v>858.55</v>
       </c>
       <c r="I34" t="n">
         <v>861.6840393228858</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>0.97</v>
+        <v>-7.07</v>
       </c>
       <c r="L34" t="n">
-        <v>7.79</v>
+        <v>8.91</v>
       </c>
       <c r="M34" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>7.96</v>
       </c>
       <c r="O34" t="n">
         <v>3.11</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.16</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44645</v>
+        <v>44648</v>
       </c>
       <c r="H35" t="n">
-        <v>920.85</v>
+        <v>943.45</v>
       </c>
       <c r="I35" t="n">
         <v>936.7980044951279</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.26</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>11</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>12.79</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H36" t="n">
-        <v>904.4</v>
+        <v>875.5</v>
       </c>
       <c r="I36" t="n">
         <v>896.4336687808143</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.14</v>
+        <v>-7.2</v>
       </c>
       <c r="L36" t="n">
-        <v>4.5</v>
+        <v>8.01</v>
       </c>
       <c r="M36" t="n">
         <v>3.27</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.75</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H37" t="n">
-        <v>803.3</v>
+        <v>822.05</v>
       </c>
       <c r="I37" t="n">
         <v>814.5224276042781</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K37" t="n">
-        <v>8.25</v>
+        <v>6.11</v>
       </c>
       <c r="L37" t="n">
         <v>2.97</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.69</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H38" t="n">
-        <v>1007.3</v>
+        <v>970.3</v>
       </c>
       <c r="I38" t="n">
         <v>979.1092736116699</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K38" t="n">
-        <v>22.54</v>
+        <v>18.03</v>
       </c>
       <c r="L38" t="n">
         <v>2.92</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.89</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44895</v>
+        <v>44896</v>
       </c>
       <c r="H39" t="n">
-        <v>923.9</v>
+        <v>960.8</v>
       </c>
       <c r="I39" t="n">
         <v>951.2716173126697</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K39" t="n">
-        <v>4.78</v>
+        <v>0.98</v>
       </c>
       <c r="L39" t="n">
         <v>4.02</v>
@@ -2664,7 +3131,7 @@
         <v>1.76</v>
       </c>
       <c r="N39" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="O39" t="n">
         <v>-3.67</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.84</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H40" t="n">
-        <v>879.3</v>
+        <v>863.25</v>
       </c>
       <c r="I40" t="n">
         <v>877.4263975237374</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.48</v>
+        <v>-10.15</v>
       </c>
       <c r="L40" t="n">
-        <v>10.43</v>
+        <v>11.22</v>
       </c>
       <c r="M40" t="n">
         <v>1.12</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.73</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H41" t="n">
-        <v>864</v>
+        <v>884.05</v>
       </c>
       <c r="I41" t="n">
         <v>869.531645928221</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.09</v>
+        <v>-2.41</v>
       </c>
       <c r="L41" t="n">
-        <v>2.87</v>
+        <v>3.56</v>
       </c>
       <c r="M41" t="n">
         <v>5.13</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.92</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H42" t="n">
-        <v>844.1</v>
+        <v>824.75</v>
       </c>
       <c r="I42" t="n">
         <v>826.4346572431634</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.52</v>
+        <v>-6.71</v>
       </c>
       <c r="L42" t="n">
-        <v>6.68</v>
+        <v>7.13</v>
       </c>
       <c r="M42" t="n">
         <v>1.27</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H43" t="n">
-        <v>862</v>
+        <v>896.75</v>
       </c>
       <c r="I43" t="n">
         <v>883.8344941446359</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.52</v>
+        <v>-8.73</v>
       </c>
       <c r="L43" t="n">
-        <v>5.06</v>
+        <v>9.25</v>
       </c>
       <c r="M43" t="n">
         <v>0.88</v>
       </c>
       <c r="N43" t="n">
-        <v>2.02</v>
+        <v>4.03</v>
       </c>
       <c r="O43" t="n">
         <v>-2.29</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45063</v>
+        <v>45064</v>
       </c>
       <c r="H44" t="n">
-        <v>914.9</v>
+        <v>890.05</v>
       </c>
       <c r="I44" t="n">
         <v>908.0249522033697</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>2.02</v>
+        <v>-0.75</v>
       </c>
       <c r="L44" t="n">
         <v>4.48</v>
       </c>
       <c r="M44" t="n">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="N44" t="n">
         <v>6.18</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.56</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45090</v>
+        <v>45091</v>
       </c>
       <c r="H45" t="n">
-        <v>984.1</v>
+        <v>1019.05</v>
       </c>
       <c r="I45" t="n">
         <v>992.9447887152705</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.57</v>
+        <v>-14.49</v>
       </c>
       <c r="L45" t="n">
-        <v>11.88</v>
+        <v>15.24</v>
       </c>
       <c r="M45" t="n">
         <v>0.62</v>
       </c>
       <c r="N45" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="O45" t="n">
         <v>-2.72</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.24</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="H46" t="n">
-        <v>1121.1</v>
+        <v>1091.05</v>
       </c>
       <c r="I46" t="n">
         <v>1110.443053146037</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K46" t="n">
-        <v>10.01</v>
+        <v>7.07</v>
       </c>
       <c r="L46" t="n">
         <v>4.32</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H47" t="n">
-        <v>1137.85</v>
+        <v>1164.7</v>
       </c>
       <c r="I47" t="n">
         <v>1157.304359306757</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.29</v>
+        <v>-6.75</v>
       </c>
       <c r="L47" t="n">
-        <v>7.14</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H48" t="n">
-        <v>1504.2</v>
+        <v>1369.75</v>
       </c>
       <c r="I48" t="n">
         <v>1429.298291948167</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K48" t="n">
-        <v>29.15</v>
+        <v>17.61</v>
       </c>
       <c r="L48" t="n">
         <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>2.93</v>
+        <v>3.94</v>
       </c>
       <c r="N48" t="n">
-        <v>3.17</v>
+        <v>8.94</v>
       </c>
       <c r="O48" t="n">
         <v>2.36</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>14.54</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H49" t="n">
-        <v>1424.75</v>
+        <v>1446.85</v>
       </c>
       <c r="I49" t="n">
         <v>1431.25120006722</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.02</v>
+        <v>-5.63</v>
       </c>
       <c r="L49" t="n">
-        <v>5.86</v>
+        <v>6.49</v>
       </c>
       <c r="M49" t="n">
         <v>1.48</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H50" t="n">
-        <v>1460.65</v>
+        <v>1399.15</v>
       </c>
       <c r="I50" t="n">
         <v>1401.400780558047</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K50" t="n">
-        <v>0.95</v>
+        <v>-3.3</v>
       </c>
       <c r="L50" t="n">
         <v>4.07</v>
@@ -3291,7 +3890,7 @@
         <v>1.49</v>
       </c>
       <c r="N50" t="n">
-        <v>2.58</v>
+        <v>4.21</v>
       </c>
       <c r="O50" t="n">
         <v>1.55</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>13.2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45426</v>
+        <v>45427</v>
       </c>
       <c r="H51" t="n">
-        <v>1519.25</v>
+        <v>1574.15</v>
       </c>
       <c r="I51" t="n">
         <v>1530.935491375605</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.58</v>
+        <v>-12.51</v>
       </c>
       <c r="L51" t="n">
-        <v>10.52</v>
+        <v>16.43</v>
       </c>
       <c r="M51" t="n">
-        <v>1.06</v>
+        <v>4.33</v>
       </c>
       <c r="N51" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="O51" t="n">
         <v>-4.21</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>11.06</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45483</v>
+        <v>45484</v>
       </c>
       <c r="H52" t="n">
-        <v>1723.65</v>
+        <v>1711.5</v>
       </c>
       <c r="I52" t="n">
         <v>1714.658809219071</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K52" t="n">
-        <v>9.5</v>
+        <v>8.73</v>
       </c>
       <c r="L52" t="n">
         <v>2.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H53" t="n">
-        <v>1827.1</v>
+        <v>1862.4</v>
       </c>
       <c r="I53" t="n">
         <v>1840.462209700301</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.75</v>
+        <v>-8.82</v>
       </c>
       <c r="L53" t="n">
-        <v>7.47</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>1.81</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.28</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H54" t="n">
-        <v>1808.4</v>
+        <v>1748.1</v>
       </c>
       <c r="I54" t="n">
         <v>1801.329223778855</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.9</v>
+        <v>-6.14</v>
       </c>
       <c r="L54" t="n">
         <v>9.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>11.39</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45575</v>
+        <v>45576</v>
       </c>
       <c r="H55" t="n">
-        <v>1879.25</v>
+        <v>1919.15</v>
       </c>
       <c r="I55" t="n">
         <v>1910.122943437168</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.5</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>8.32</v>
+        <v>10.11</v>
       </c>
       <c r="M55" t="n">
         <v>0.86</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.23</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H56" t="n">
-        <v>2128.3</v>
+        <v>2013.35</v>
       </c>
       <c r="I56" t="n">
         <v>2103.413477364105</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K56" t="n">
-        <v>10.9</v>
+        <v>4.91</v>
       </c>
       <c r="L56" t="n">
         <v>3.67</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>14.64</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45768</v>
+        <v>45769</v>
       </c>
       <c r="H57" t="n">
-        <v>1656.2</v>
+        <v>1699.7</v>
       </c>
       <c r="I57" t="n">
         <v>1668.754867496894</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K57" t="n">
-        <v>17.74</v>
+        <v>15.58</v>
       </c>
       <c r="L57" t="n">
         <v>5.5</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.37</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H58" t="n">
-        <v>1835.5</v>
+        <v>1804.2</v>
       </c>
       <c r="I58" t="n">
         <v>1826.734595597746</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K58" t="n">
-        <v>7.99</v>
+        <v>6.15</v>
       </c>
       <c r="L58" t="n">
         <v>11.16</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H59" t="n">
-        <v>1687.1</v>
+        <v>1700.5</v>
       </c>
       <c r="I59" t="n">
         <v>1689.308160433181</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K59" t="n">
-        <v>6.49</v>
+        <v>5.75</v>
       </c>
       <c r="L59" t="n">
         <v>2.93</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.46</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="H60" t="n">
-        <v>1708.5</v>
+        <v>1655.4</v>
       </c>
       <c r="I60" t="n">
         <v>1683.189017518824</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K60" t="n">
-        <v>0.47</v>
+        <v>-2.65</v>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>3.03</v>
       </c>
       <c r="M60" t="n">
         <v>1.15</v>
       </c>
       <c r="N60" t="n">
-        <v>1.99</v>
+        <v>3.11</v>
       </c>
       <c r="O60" t="n">
         <v>0.79</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.91</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H61" t="n">
-        <v>1519.9</v>
+        <v>1560.3</v>
       </c>
       <c r="I61" t="n">
         <v>1554.313595242073</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K61" t="n">
-        <v>8.19</v>
+        <v>5.74</v>
       </c>
       <c r="L61" t="n">
         <v>6.14</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>6</v>
+      </c>
+      <c r="U61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>12.58</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H62" t="n">
-        <v>1861.1</v>
+        <v>1778.8</v>
       </c>
       <c r="I62" t="n">
         <v>1810.1190039404</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K62" t="n">
-        <v>19.28</v>
+        <v>14</v>
       </c>
       <c r="L62" t="n">
         <v>3.94</v>
@@ -3975,7 +4718,7 @@
         <v>3.06</v>
       </c>
       <c r="N62" t="n">
-        <v>4.01</v>
+        <v>4.42</v>
       </c>
       <c r="O62" t="n">
         <v>2.66</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>9.99</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="H63" t="n">
-        <v>1846</v>
+        <v>1931</v>
       </c>
       <c r="I63" t="n">
         <v>1904.890650520174</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.78</v>
+        <v>-8.56</v>
       </c>
       <c r="L63" t="n">
-        <v>4.73</v>
+        <v>9.4</v>
       </c>
       <c r="M63" t="n">
         <v>0.49</v>
       </c>
       <c r="N63" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="O63" t="n">
         <v>-4.42</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="H64" t="n">
-        <v>1792</v>
+        <v>1741.1</v>
       </c>
       <c r="I64" t="n">
         <v>1767.129123897376</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.2</v>
+        <v>-9.83</v>
       </c>
       <c r="L64" t="n">
-        <v>7.95</v>
+        <v>11.2</v>
       </c>
       <c r="M64" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="N64" t="n">
         <v>3.78</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H65" t="n">
-        <v>1821</v>
+        <v>1845.6</v>
       </c>
       <c r="I65" t="n">
         <v>1838.43828760017</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.59</v>
+        <v>-6</v>
       </c>
       <c r="L65" t="n">
-        <v>4.97</v>
+        <v>6.43</v>
       </c>
       <c r="M65" t="n">
         <v>0.28</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>9.57</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="H66" t="n">
-        <v>1736</v>
+        <v>1663.3</v>
       </c>
       <c r="I66" t="n">
         <v>1703.215387354531</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.94</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>6.45</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M66" t="n">
         <v>1.89</v>
       </c>
       <c r="N66" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="O66" t="n">
         <v>1.35</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>14</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9221,7 +10032,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -9231,7 +10042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9241,7 +10052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -9251,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9261,7 +10072,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -9271,7 +10082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -9281,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -9291,7 +10102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -9301,7 +10112,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.8</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="14">
@@ -9311,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.62</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="15">
@@ -9321,7 +10132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="16">
@@ -9331,7 +10142,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.07</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="17">
@@ -9341,7 +10152,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>46.64</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +10162,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="19">
@@ -9361,7 +10172,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.029999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -9371,7 +10182,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.81</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +10192,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.69</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="22">
@@ -9391,7 +10202,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -9401,7 +10212,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -9411,7 +10222,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="25">
@@ -9421,7 +10232,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.76</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="26">
@@ -9431,7 +10242,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.89</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="27">
@@ -9441,7 +10252,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.89</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="28">
@@ -9451,7 +10262,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
